--- a/education_surveys/017_educational_support_assessment--education_surveys.xlsx
+++ b/education_surveys/017_educational_support_assessment--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,8 +869,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,12 +898,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'lack_of_interest_in_the_subject',_'label':_'lack_of_interest_in_the_subject'}</t>
+          <t>lack_of_interest_in_the_subject</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'lack of interest in the subject', 'label': 'lack of interest in the subject'}</t>
+          <t>lack of interest in the subject</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'difficulty_keeping_up_with_the_pace',_'label':_'difficulty_keeping_up_with_the_pace'}</t>
+          <t>difficulty_keeping_up_with_the_pace</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'difficulty keeping up with the pace', 'label': 'difficulty keeping up with the pace'}</t>
+          <t>difficulty keeping up with the pace</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'personal_issues',_'label':_'personal_issues'}</t>
+          <t>personal_issues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'personal issues', 'label': 'personal issues'}</t>
+          <t>personal issues</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'lack_of_support_from_teachers_or_peers',_'label':_'lack_of_support_from_teachers_or_peers'}</t>
+          <t>lack_of_support_from_teachers_or_peers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'lack of support from teachers or peers', 'label': 'lack of support from teachers or peers'}</t>
+          <t>lack of support from teachers or peers</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'lack_of_access_to_resources',_'label':_'lack_of_access_to_resources'}</t>
+          <t>lack_of_access_to_resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'lack of access to resources', 'label': 'lack of access to resources'}</t>
+          <t>lack of access to resources</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'time_management',_'label':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'time management', 'label': 'time management'}</t>
+          <t>time management</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'organization_skills',_'label':_'organization_skills'}</t>
+          <t>organization_skills</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'organization skills', 'label': 'organization skills'}</t>
+          <t>organization skills</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'communication_skills',_'label':_'communication_skills'}</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'communication skills', 'label': 'communication skills'}</t>
+          <t>communication skills</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'self_confidence',_'label':_'self-confidence'}</t>
+          <t>self-confidence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'self confidence', 'label': 'self-confidence'}</t>
+          <t>self-confidence</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'improve_grades',_'label':_'improve_grades'}</t>
+          <t>improve_grades</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'improve grades', 'label': 'improve grades'}</t>
+          <t>improve grades</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'improve_engagement',_'label':_'improve_engagement'}</t>
+          <t>improve_engagement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'improve engagement', 'label': 'improve engagement'}</t>
+          <t>improve engagement</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'time_management',_'label':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'time management', 'label': 'time management'}</t>
+          <t>time management</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'organization_skills',_'label':_'organization_skills'}</t>
+          <t>organization_skills</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'organization skills', 'label': 'organization skills'}</t>
+          <t>organization skills</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'communication_skills',_'label':_'communication_skills'}</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'communication skills', 'label': 'communication skills'}</t>
+          <t>communication skills</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'self_confidence',_'label':_'self-confidence'}</t>
+          <t>self-confidence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'self confidence', 'label': 'self-confidence'}</t>
+          <t>self-confidence</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'english', 'label': 'english'}</t>
+          <t>english</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chinese',_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chinese', 'label': 'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'spanish', 'label': 'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'english', 'label': 'english'}</t>
+          <t>english</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chinese',_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chinese', 'label': 'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'spanish', 'label': 'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'english', 'label': 'english'}</t>
+          <t>english</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chinese',_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chinese', 'label': 'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'spanish', 'label': 'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
